--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.78979361912579</v>
+        <v>8.090841463107941</v>
       </c>
       <c r="D2" t="n">
-        <v>60.41229119198876</v>
+        <v>9.816997318698172</v>
       </c>
       <c r="E2" t="n">
-        <v>13.0055564974563</v>
+        <v>2.113402930836649</v>
       </c>
       <c r="F2" t="n">
-        <v>9.248740874849823</v>
+        <v>1.502920392163096</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.80909770268568</v>
+        <v>7.768978376686424</v>
       </c>
       <c r="D3" t="n">
-        <v>38.70451802225639</v>
+        <v>6.289484178616664</v>
       </c>
       <c r="E3" t="n">
-        <v>13.0055564974563</v>
+        <v>2.113402930836649</v>
       </c>
       <c r="F3" t="n">
-        <v>9.248740874849823</v>
+        <v>1.502920392163096</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.61874249940087</v>
+        <v>2.538045656152641</v>
       </c>
       <c r="D4" t="n">
-        <v>54.37402541195406</v>
+        <v>8.835779129442535</v>
       </c>
       <c r="E4" t="n">
-        <v>13.0055564974563</v>
+        <v>2.113402930836649</v>
       </c>
       <c r="F4" t="n">
-        <v>9.248740874849823</v>
+        <v>1.502920392163096</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.99971670603669</v>
+        <v>3.087453964730963</v>
       </c>
       <c r="D5" t="n">
-        <v>59.47634242105496</v>
+        <v>9.664905643421431</v>
       </c>
       <c r="E5" t="n">
-        <v>13.0055564974563</v>
+        <v>2.113402930836649</v>
       </c>
       <c r="F5" t="n">
-        <v>9.248740874849823</v>
+        <v>1.502920392163096</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.75726262247034</v>
+        <v>5.32305517615143</v>
       </c>
       <c r="D6" t="n">
-        <v>64.84210243544165</v>
+        <v>10.53684164575927</v>
       </c>
       <c r="E6" t="n">
-        <v>13.0055564974563</v>
+        <v>2.113402930836649</v>
       </c>
       <c r="F6" t="n">
-        <v>9.248740874849823</v>
+        <v>1.502920392163096</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.30569293158523</v>
+        <v>6.062175101382601</v>
       </c>
       <c r="D7" t="n">
-        <v>66.66221059487732</v>
+        <v>10.83260922166757</v>
       </c>
       <c r="E7" t="n">
-        <v>13.0055564974563</v>
+        <v>2.113402930836649</v>
       </c>
       <c r="F7" t="n">
-        <v>9.248740874849823</v>
+        <v>1.502920392163096</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
